--- a/MINAGRIS_Plastic.R_ReadMe.xlsx
+++ b/MINAGRIS_Plastic.R_ReadMe.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\berio001\Documents\MINAGRIS_C\MINAGRIS_Microplastic_Soil_Assessmnent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B45BA00-4512-4391-BCFF-FD57EC2A8220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A995F3AE-9E9F-45CC-9054-07AACA89C711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A634431C-1F0B-4477-A9DD-2C46E099AE2B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{A634431C-1F0B-4477-A9DD-2C46E099AE2B}"/>
   </bookViews>
   <sheets>
     <sheet name="Scripts" sheetId="1" r:id="rId1"/>
@@ -1354,6 +1354,60 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1507375</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>-1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>557729</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>103973</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F94CF7AF-4A50-FFD6-F1AB-6B3111A01FB4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7603375" y="3782290"/>
+          <a:ext cx="12142899" cy="3886265"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2513,6 +2567,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/MINAGRIS_Plastic.R_ReadMe.xlsx
+++ b/MINAGRIS_Plastic.R_ReadMe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\berio001\Documents\MINAGRIS_C\MINAGRIS_Microplastic_Soil_Assessmnent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A995F3AE-9E9F-45CC-9054-07AACA89C711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E150080-8BE2-43DF-87CE-192B9B3B9032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{A634431C-1F0B-4477-A9DD-2C46E099AE2B}"/>
   </bookViews>
@@ -287,9 +287,6 @@
   </si>
   <si>
     <t>m20_1111_n_f1</t>
-  </si>
-  <si>
-    <t>IR_Name</t>
   </si>
   <si>
     <t>Name of the raw data IR folder</t>
@@ -1080,6 +1077,9 @@
   </si>
   <si>
     <t>Mean (Soil) per Lab</t>
+  </si>
+  <si>
+    <t>IR_name</t>
   </si>
 </sst>
 </file>
@@ -1361,13 +1361,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1507375</xdr:colOff>
+      <xdr:colOff>1313412</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>-1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>557729</xdr:colOff>
+      <xdr:colOff>363766</xdr:colOff>
       <xdr:row>42</xdr:row>
       <xdr:rowOff>103973</xdr:rowOff>
     </xdr:to>
@@ -1392,7 +1392,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7603375" y="3782290"/>
+          <a:off x="7409412" y="3782290"/>
           <a:ext cx="12142899" cy="3886265"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1721,7 +1721,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>10</v>
@@ -1747,56 +1747,56 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C2" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="E2" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="D2" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>163</v>
-      </c>
       <c r="F2" s="28" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="17" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F3" s="28" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C4" s="17" t="s">
         <v>165</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>166</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="17"/>
       <c r="F4" s="22" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -1804,10 +1804,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>17</v>
@@ -1816,7 +1816,7 @@
         <v>18</v>
       </c>
       <c r="F5" s="28" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1827,19 +1827,19 @@
         <v>0</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1859,7 +1859,7 @@
         <v>21</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1879,7 +1879,7 @@
         <v>22</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
@@ -1920,7 +1920,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>10</v>
@@ -1955,7 +1955,7 @@
         <v>16</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -1972,34 +1972,34 @@
         <v>29</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F16" s="24"/>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="23" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>25</v>
@@ -2008,7 +2008,7 @@
         <v>18</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -2270,94 +2270,94 @@
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B15" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="D15" s="8" t="s">
         <v>181</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>182</v>
       </c>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B16" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="D16" s="8" t="s">
         <v>83</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>84</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>80</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="D17" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="E17" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="F17" s="9" t="s">
         <v>89</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="D18" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="E18" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="E18" s="9" t="s">
-        <v>94</v>
-      </c>
       <c r="F18" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="D19" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="E19" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="F19" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="D20" s="8" t="s">
         <v>101</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>102</v>
       </c>
       <c r="E20" s="9">
         <v>756</v>
@@ -2368,13 +2368,13 @@
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="D21" s="8" t="s">
         <v>104</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>105</v>
       </c>
       <c r="E21" s="9">
         <v>88.8</v>
@@ -2385,10 +2385,10 @@
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="C22" s="10" t="s">
         <v>106</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>107</v>
       </c>
       <c r="D22" s="10" t="s">
         <v>48</v>
@@ -2398,169 +2398,169 @@
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="C23" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="C23" s="12" t="s">
-        <v>109</v>
-      </c>
       <c r="D23" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C24" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="D24" s="12" t="s">
         <v>111</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>112</v>
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B25" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C25" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="C25" s="12" t="s">
-        <v>114</v>
-      </c>
       <c r="D25" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C26" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="C26" s="12" t="s">
-        <v>116</v>
-      </c>
       <c r="D26" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B27" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C27" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="C27" s="12" t="s">
-        <v>118</v>
-      </c>
       <c r="D27" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C28" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="D28" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="C29" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="C29" s="12" t="s">
-        <v>123</v>
-      </c>
       <c r="D29" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="C30" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="C30" s="12" t="s">
-        <v>125</v>
-      </c>
       <c r="D30" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B31" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="C31" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="C31" s="12" t="s">
-        <v>127</v>
-      </c>
       <c r="D31" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B32" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="C32" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="C32" s="12" t="s">
-        <v>129</v>
-      </c>
       <c r="D32" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B33" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C33" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="C33" s="12" t="s">
-        <v>131</v>
-      </c>
       <c r="D33" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B34" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="C34" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="D34" s="12" t="s">
         <v>133</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>134</v>
       </c>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B35" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="C35" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="C35" s="12" t="s">
-        <v>136</v>
-      </c>
       <c r="D35" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
@@ -2594,7 +2594,7 @@
         <v>32</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>33</v>
@@ -2611,7 +2611,7 @@
         <v>36</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>37</v>
@@ -2631,7 +2631,7 @@
         <v>43</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>44</v>
@@ -2645,16 +2645,16 @@
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" s="26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>47</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>49</v>
@@ -2671,7 +2671,7 @@
         <v>52</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>53</v>
@@ -2691,7 +2691,7 @@
         <v>57</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>58</v>
@@ -2711,7 +2711,7 @@
         <v>62</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>63</v>
@@ -2728,13 +2728,13 @@
         <v>64</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F8" s="9">
         <v>7</v>
@@ -2748,13 +2748,13 @@
         <v>67</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F9" s="9">
         <v>1</v>
@@ -2768,13 +2768,13 @@
         <v>70</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F10" s="9">
         <v>1</v>
@@ -2785,22 +2785,22 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B11" s="26" t="s">
+        <v>228</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="D11" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="F11" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="F11" s="9" t="s">
+      <c r="G11" s="9" t="s">
         <v>231</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.3">
@@ -2811,7 +2811,7 @@
         <v>74</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>75</v>
@@ -2831,10 +2831,10 @@
         <v>78</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>80</v>
@@ -2845,89 +2845,89 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B14" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>181</v>
-      </c>
       <c r="D14" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B15" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="D15" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="E15" s="8" t="s">
+      <c r="F15" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="G15" s="9" t="s">
         <v>89</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B16" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="D16" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="D16" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="E16" s="8" t="s">
+      <c r="F16" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="F16" s="9" t="s">
-        <v>94</v>
-      </c>
       <c r="G16" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="D17" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="D17" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="E17" s="8" t="s">
+      <c r="F17" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="G17" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>107</v>
-      </c>
       <c r="D18" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>48</v>
@@ -2937,176 +2937,176 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B20" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="D20" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="E20" s="12" t="s">
         <v>111</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>259</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>112</v>
       </c>
       <c r="F20" s="11"/>
       <c r="G20" s="11"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="C21" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="C21" s="12" t="s">
-        <v>114</v>
-      </c>
       <c r="D21" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F21" s="11"/>
       <c r="G21" s="11"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B22" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="C22" s="12" t="s">
-        <v>116</v>
-      </c>
       <c r="D22" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F22" s="11"/>
       <c r="G22" s="11"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B23" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="C23" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="C23" s="12" t="s">
-        <v>118</v>
-      </c>
       <c r="D23" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F23" s="11"/>
       <c r="G23" s="11"/>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B24" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="C24" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="C24" s="12" t="s">
-        <v>123</v>
-      </c>
       <c r="D24" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F24" s="11"/>
       <c r="G24" s="11"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B25" s="13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F25" s="11"/>
       <c r="G25" s="11"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B26" s="13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F26" s="11"/>
       <c r="G26" s="11"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B27" s="13" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F27" s="11"/>
       <c r="G27" s="11"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B28" s="13" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C28" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="E28" s="12" t="s">
         <v>133</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>134</v>
       </c>
       <c r="F28" s="11"/>
       <c r="G28" s="11"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B29" s="13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F29" s="11"/>
       <c r="G29" s="11"/>
@@ -3133,24 +3133,24 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="C1" s="14" t="s">
         <v>151</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>152</v>
       </c>
       <c r="D1" s="14"/>
       <c r="E1" s="29"/>
       <c r="F1" s="14" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -3158,19 +3158,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -3181,19 +3181,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I3">
         <v>2</v>
@@ -3201,13 +3201,13 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="F4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I4">
         <v>3</v>
@@ -3218,19 +3218,19 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I5">
         <v>4</v>
@@ -3241,19 +3241,19 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I6">
         <v>5</v>
@@ -3267,16 +3267,16 @@
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F7" t="s">
         <v>70</v>
       </c>
       <c r="G7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I7">
         <v>6</v>
@@ -3290,16 +3290,16 @@
         <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F8" t="s">
         <v>67</v>
       </c>
       <c r="G8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I8">
         <v>7</v>
@@ -3313,16 +3313,16 @@
         <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F9" t="s">
         <v>64</v>
       </c>
       <c r="G9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I9">
         <v>8</v>
@@ -3333,19 +3333,19 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I10">
         <v>9</v>
@@ -3356,19 +3356,19 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C11" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G11" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H11" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I11">
         <v>10</v>
@@ -3382,16 +3382,16 @@
         <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F12" t="s">
         <v>42</v>
       </c>
       <c r="G12" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H12" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I12">
         <v>11</v>
@@ -3402,90 +3402,90 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C14" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C15" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C16" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C19" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="C20" t="s">
         <v>155</v>
-      </c>
-      <c r="C20" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="C21" t="s">
         <v>173</v>
-      </c>
-      <c r="C21" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="C22" t="s">
         <v>176</v>
-      </c>
-      <c r="C22" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="C23" t="s">
         <v>218</v>
-      </c>
-      <c r="C23" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C24" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -3516,7 +3516,7 @@
         <v>32</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -3527,7 +3527,7 @@
         <v>36</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>37</v>
@@ -3541,7 +3541,7 @@
         <v>43</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>44</v>
@@ -3549,16 +3549,16 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>47</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -3569,7 +3569,7 @@
         <v>52</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>53</v>
@@ -3583,7 +3583,7 @@
         <v>57</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>58</v>
@@ -3597,7 +3597,7 @@
         <v>62</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>63</v>
@@ -3608,13 +3608,13 @@
         <v>64</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -3622,13 +3622,13 @@
         <v>67</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -3636,27 +3636,27 @@
         <v>70</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="26" t="s">
+        <v>228</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>230</v>
-      </c>
       <c r="C11" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -3667,7 +3667,7 @@
         <v>74</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>75</v>
@@ -3681,206 +3681,206 @@
         <v>78</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>181</v>
-      </c>
       <c r="C14" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="C15" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>87</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="C16" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>92</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="C17" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>96</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -3898,15 +3898,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -3922,7 +3922,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -3938,7 +3938,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -3946,7 +3946,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B7">
         <v>2</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B8">
         <v>2</v>
@@ -3962,7 +3962,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -3970,7 +3970,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B10">
         <v>2</v>
@@ -3978,7 +3978,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B11">
         <v>2</v>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B12">
         <v>2</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="25" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B13" s="25">
         <v>4</v>
@@ -4002,7 +4002,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="25" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B14" s="25">
         <v>6</v>
@@ -4010,7 +4010,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B15">
         <v>7</v>
@@ -4018,7 +4018,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B16">
         <v>9</v>
@@ -4026,7 +4026,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B17">
         <v>10</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B18">
         <v>11</v>
@@ -4042,7 +4042,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B19">
         <v>11</v>
@@ -4050,7 +4050,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B20">
         <v>12</v>
@@ -4058,7 +4058,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B21">
         <v>13</v>
@@ -4066,7 +4066,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B22">
         <v>14</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B23">
         <v>18</v>
@@ -4082,7 +4082,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B24">
         <v>41</v>
@@ -4090,7 +4090,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B25">
         <v>42</v>
